--- a/data/export/completed_contacts.xlsx
+++ b/data/export/completed_contacts.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,134 +425,146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="43" customWidth="1" min="9" max="9"/>
-    <col width="37" customWidth="1" min="10" max="10"/>
-    <col width="38" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="50" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Business Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Official Website</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Emails</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Phones</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Extraction Method</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Pages Visited</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Twitter</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Provenance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Farallon Capital Management, L.L.C.</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.healthgrades.com/physician/dr-suyu-zhang-ynk6</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>https://www.faralloncapital.com/contact-us</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>asiamediainquiries@faralloncapital.com, irinquiries@faralloncapital.com, mediainquiries@faralloncapital.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+12125972270, +14154212132, +442073957200, +551120509303, +6563382132, +81364501991, +85225970100</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>224 S. MICHIGAN AVENUE, New York, NY, IL</t>
+          <t>c/o Farallon Capital Management, San Francisco, CA, CA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Browser</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.healthgrades.com/physician/dr-suyu-zhang-ynk6</t>
+          <t>https://www.faralloncapital.com/contact-us</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -552,26 +576,34 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Weaver Mine Capital Management Hedge Fund Manager Profile</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/ny/new-york/profile/financial-services/zenquant-technologies-lp-0633-90004641</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>https://www.preqin.com/data/profile/fund-manager/weaver-mine-capital-management/533018</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>preqin.clientservices@blackrock.com, preqin.info@blackrock.com, press@preqin.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+12122030200, +12122034500</t>
+          <t>+442036493276</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11622 El Camino Real, New York, NY, CA</t>
+          <t>403 WEAVER MINE TRAIL, Chapel Hill, North Carolina, US</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -580,54 +612,66 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.bbb.org/us/ny/new-york/profile/financial-services/zenquant-technologies-lp-0633-90004641, https://www.bbb.org/us/ny/new-york/profile/fintech/zenquant-fintech-llc-1256-90004641, https://www.bbb.org/us/ny/new-york/profile/venture-capital/zelda-ventures-gp-1-llc-1256-900001, https://www.bbb.org/us/ny/new-york/profile/venture-capital/zelda-ventures-gp-2-llc-1256c-100000000</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+          <t>https://www.preqin.com/about/who-we-are, https://www.preqin.com/contact-us, https://www.preqin.com/data/profile/fund-manager/weaver-mine-capital-management/533018, https://www.preqin.com/preqins-research-insights-content-teams</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/147822/</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/people/Preqin/100063552974258/</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/preqin</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://x.com/preqin</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCOSSwdWLWEDF-_audb5S_fw</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>AI Reasoning: The phone number was retrieved directly from the official Better Business Bureau profile for ZenQuant Fintech LLC.; AI Reasoning: The phone number was retrieved from the official Better Business Bureau profile for Zelda Ventures GP 2 LLC. No official email address was explicitly listed on the provided profile page.</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{"business_name": "scraper", "emails": "", "phones": ",AI", "address": "importer"}</t>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NPPES NPI Registry</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://npiregistry.cms.hhs.gov/registry</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1813520/000181352020000002/xslFormDX01/primary_doc.xml</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>customerservicenpienumerator@cms.hhs.gov, customerservice@npienumerate.com</t>
+          <t>form@sipc.org, mike@cogepa.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+18004653203, +18006922326</t>
+          <t>+16303518942, +16464729603</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c/o Intus Care Inc., Nashville, TN, RI</t>
+          <t>4370 Alpine Road, Los Altos, CA, US</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -636,11 +680,11 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://npiregistry.cms.hhs.gov/registry, https://npiregistry.cms.hhs.gov/contact, https://npiregistry.cms.hhs.gov/contact-us, https://npiregistry.cms.hhs.gov/about</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1214044/000101359418000566/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1297389/000129738919000002/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1812095/000090514821000596/efc21-459_sc13d.htm, https://www.sec.gov/Archives/edgar/data/1813520/000181352020000002/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1843541/000119248221000123/xslFormDX08/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1887390/0001879785-21-000005-index.htm, https://www.sec.gov/Archives/edgar/data/1974893/000197489325000002/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2104310/000109690626000046/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/vprr/1800/18005703.pdf</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -651,100 +695,76 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>AI Reasoning: The NPI Registry is a CMS-managed service. The official help desk contact information is provided through the NPI Enumerator support channels associated with the CMS NPI Registry portal.</t>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.; AI Enrichment Error: No AI providers available for structured query.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{"business_name": "scraper", "emails": "scraper,AI", "phones": "scraper", "address": "importer"}</t>
+          <t>{"business_name": "scraper", "emails": ",scraper", "phones": ",scraper", "address": "importer"}</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Eric Weitner - Global Head Of Technology Operations at Weber Shandwick</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://theorg.com/org/weber-shandwick/org-chart/eric-weitner</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>pr@theorg.com, sales@theorg.com</t>
-        </is>
-      </c>
+          <t>https://www.bbb.org/us/wa/woodinville/profile/boat-dealers/three-rivers-marine-1296-22025154</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>96 Anderson Street, New York, United States, US</t>
+          <t>6929 North Hayden Road, Woodinville, Washington, AZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Merged</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://theorg.com/org/weber-shandwick/org-chart/eric-weitner, https://theorg.com/contact, https://theorg.com/about, https://theorg.com/contact-us</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/theorg/</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/theorgcom</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/theorgcom</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://x.com/theorgcom</t>
-        </is>
-      </c>
+          <t>https://www.bbb.org/us/ny/new-york/profile/financial-services/zenquant-technologies-lp-0633-90004641, https://www.bbb.org/us/ny/new-york/profile/fintech/zenquant-fintech-llc-1256-90004641, https://www.bbb.org/us/ny/new-york/profile/venture-capital/zelda-ventures-gp-1-llc-1256-900001, https://www.bbb.org/us/ny/new-york/profile/venture-capital/zelda-ventures-gp-2-llc-1256c-100000000, https://www.bbb.org/us/wa/woodinville/profile/boat-dealers/three-rivers-marine-1296-22025154</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Blair WELCH personal appointments</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/officers/RuC8OydjAEfPQ9ZKyAxboSSacfY/appointments</t>
+          <t>https://www.loopnet.com/commercial-real-estate-brokers/profile/joseph-weiss/kp6lx68b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>c/o Slate Asset Management, Toronto, Ontario, IL</t>
+          <t>80 Sherman Street, Montvale, NJ, US</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Browser</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -752,7 +772,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/officers/RuC8OydjAEfPQ9ZKyAxboSSacfY/appointments, https://find-and-update.company-information.service.gov.uk/help/cookies, https://find-and-update.company-information.service.gov.uk/help/accessibility-statement, https://find-and-update.company-information.service.gov.uk/officers/RuC8OydjAEfPQ9ZKyAxboSSacfY/appointments#content, https://find-and-update.company-information.service.gov.uk/help/feedback?sourceurl=https://find-and-update.company-information.service.gov.uk/officers/RuC8OydjAEfPQ9ZKyAxboSSacfY/appointments</t>
+          <t>https://www.loopnet.com/commercial-real-estate-brokers/profile/joseph-weiss/kp6lx68b</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -768,6 +788,3850 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://marketcast.smartkarma.com/company/green-options-pbc</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>712 SE 7th Avenue, Portland, OR, US</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://marketcast.smartkarma.com/company/green-options-pbc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://hig.com/team/george-webster</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>200 W. Martin Luther King Blvd., New York, NY, TN</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://hig.com/team/george-webster</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AngelBacked</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.angelbacked.co/investor/larry-weidman</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>700 River Avenue, Pittsburgh, Pennsylvania, PA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.angelbacked.co/investor/larry-weidman, https://www.angelbacked.co/contact, https://www.angelbacked.co/contact-us, https://www.angelbacked.co/about</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://x.com/angelbackedco</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.nasaaefd.org/FormD/primaryDocument</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2345 E. 3rd Avenue, Denver, Colorado, CO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.nasaaefd.org/FormD/primaryDocument</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>About Us</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://edibleschoolyard.org/about-us</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ashley@edibleschoolyard.org, jennifer@alicewatersinstitute.org, jeremy@edibleschoolyard.org, kathryn@alicewatersinstitute.org, schoolyard@dr.martin</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>+15103886371, +15108433811</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Room 5A01, Berkeley, California, F4</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://edibleschoolyard.org/about-us, https://edibleschoolyard.org/content/contact-us, https://edibleschoolyard.org/about-us, https://edibleschoolyard.org/about-us#off-canvas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/edibleschoolyard/?hl=en</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Edibleschoolyrd</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Eric Weitner - Global Head Of Technology Operations at Weber Shandwick</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://theorg.com/org/weber-shandwick/org-chart/eric-weitner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pr@theorg.com, sales@theorg.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>96 Anderson Street, New York, United States, US</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://theorg.com/org/weber-shandwick/org-chart/eric-weitner, https://theorg.com/contact, https://theorg.com/about, https://theorg.com/contact-us</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/theorg/</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/theorgcom</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/theorgcom</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://x.com/theorgcom</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Blair WELCH personal appointments</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/officers/RuC8OydjAEfPQ9ZKyAxboSSacfY/appointments</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c/o Slate Asset Management, Toronto, Ontario, IL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/officers/RuC8OydjAEfPQ9ZKyAxboSSacfY/appointments, https://find-and-update.company-information.service.gov.uk/help/cookies, https://find-and-update.company-information.service.gov.uk/help/accessibility-statement, https://find-and-update.company-information.service.gov.uk/officers/RuC8OydjAEfPQ9ZKyAxboSSacfY/appointments#content</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://m3property.com.au/static/016dbe8b1c7fd41ce4da05be50aa95a2/M3-Property-Insight-SDA-Price-Review-June-2023-1.pdf</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>infonsw@m3property.com.au, infoqld@m3property.com.au, infosa@m3property.com.au, infovic@m3property.com.au</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>+17053381989, +18103005437, +61282348100, +61396051000, +61736207900, +61870991800</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>The Grange, Sydney, NSW, X0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://m3property.com.au/static/016dbe8b1c7fd41ce4da05be50aa95a2/M3-Property-Insight-SDA-Price-Review-June-2023-1.pdf, https://m3property.com.au/contact, https://m3property.com.au/contact-us, https://m3property.com.au/about</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://au.linkedin.com/company/m3property</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rui Wei</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://chem.scu.edu.cn/hxen/info/1027/1967.htm</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>chem@scu.edu.cn, weir@scu.edu.cn</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>+13807381419, +14703471014, +16782678513, +17603761223, +17723772922, +19567957221, +19796981017, +862885412290, +862885412291</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>30 Montgomery St, Chengdu, Sichuan, NJ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://chem.scu.edu.cn/hxen/info/1027/1967.htm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OTC Markets</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://www.otcmarkets.com/stock/MUNMF/profile</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1040 West Georgia Street, Vancouver, BC, A1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Merged</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.otcmarkets.com/about, https://www.otcmarkets.com/contact, https://www.otcmarkets.com/contact-us, https://www.otcmarkets.com/stock/CMRB/profile, https://www.otcmarkets.com/stock/MUNMF/profile</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Europe Startup News: Revolut, Elvy, APEX</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.startupresearcher.com/news/startup-researcher-europe-week-50-2025</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Kungsklippan 11, Stockholm, Stockholm, US</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.startupresearcher.com/news/startup-researcher-europe-week-50-2025, https://www.startupresearcher.com/contact-us, https://www.startupresearcher.com/about-us, https://www.startupresearcher.com/news/kbc-group-launches-100-million-fund-to-support-belgian-startups</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/startup-researcher</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://x.com/SR_Researcher_</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Who We Are</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://pgsa.com/who-we-are</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>info@pgsa.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>+14029919482</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1536 Cuming Street, Omaha, Nebraska, US</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://pgsa.com/who-we-are</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pgsallc/</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>School Partnership Lead in Swansea at Swansea University</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://talents.studysmarter.co.uk/companies/swansea-university/school-partnership-lead-15039983</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>andrew.townsend@swansea.ac.uk, j.a.wedlake@swansea.ac.uk</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Windward 3, Swansea, Wales, E9</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://talents.studysmarter.co.uk/companies/swansea-university/school-partnership-lead-15039983, https://talents.studysmarter.co.uk/jobs/, https://talents.studysmarter.co.uk/contact, https://talents.studysmarter.co.uk/contact-us</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/studysmarter/</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/StudySmarter.de</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/studysmarter/</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://twitter.com/studysmarterDE/</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://www.tuftsmedicine.org/doctor/harry-webster</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>80 HINES RD, Billerica, Massachusetts, A6</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.tuftsmedicine.org/doctor/harry-webster</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Client Challenge</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.houzz.com/professionals/architects-and-building-designers/rc-wehmeyer-design-build-pfvwus-pf~1704441297</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1835B Kramer Ln, Burlingame, CA, TX</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.houzz.com/professionals/architects-and-building-designers/rc-wehmeyer-design-build-pfvwus-pf~1704441297, https://www.houzz.com/contact, https://www.houzz.com/contact-us, https://www.houzz.com/about</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Boaz Ronald Weinstein</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://privatefunddata.com/fund-employees/boaz-ronald-weinstein-2642143</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>hello@privatefunddata.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>405 Lexington Avenue, New York, NY, NY</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://privatefunddata.com/fund-employees/boaz-ronald-weinstein-2642143, https://privatefunddata.com/contact/, https://privatefunddata.com/contact, https://privatefunddata.com/contact-us</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Richard J. Watson - EY Global Consulting Cybersecurity Leader</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.ey.com/en_ug/people/richard-watson</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ai@scale.ey</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>550 East Swedesford Rd. Suite 350, Sydney, Australia, US</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.ey.com/en_ug/people/richard-watson, https://www.ey.com/en_gl/locations, https://www.ey.com/en_gl/about-us, https://www.ey.com/en_gl/board-matters</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richardwatsoncybersecurity/</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/pages/Ernst-Young/195665063800329</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://www.twitter.com/Watsoncyber</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Samuel-Wathen</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1441 Brickell Avenue, Conway, South Carolina, FL</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.researchgate.net/profile/Samuel-Wathen</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://www.fsc.gi/regulated-entity/waystone-management-company-ie-limited-29796</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3rd Floor, Dublin, Ireland, L2</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.fsc.gi/regulated-entity/waystone-management-company-ie-limited-29796</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://www.michaelweinstock.com/contact</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>535 Madison Avenue, Niceville, FL, US</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.michaelweinstock.com/contact</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.accessnewswire.com/newsroom/en/computers-technology-and-internet/setsale-closes-2-million-to-bring-ai-efficiency-to-the-hvac-suppl-1146873</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>418 ATHERTON ST., Charlotte, North Carolina, US</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.accessnewswire.com/newsroom/en/computers-technology-and-internet/setsale-closes-2-million-to-bring-ai-efficiency-to-the-hvac-suppl-1146873</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WEEKEND FUND IV, LP</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.formds.com/issuers/weekend-fund-iv-lp</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>+13603409337</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>5701 Biscayne Boulevard, Miami, Florida, FL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.formds.com/issuers/weekend-fund-iv-lp, https://www.formds.com/contact, https://www.formds.com/contact-us, https://www.formds.com/about</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.dougweide100summitdrivesyndicationsandimmersivelodging.com</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>100 Summit Drive, 100 Summit Drive, syndications and immersive lodging, US</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.dougweide100summitdrivesyndicationsandimmersivelodging.com</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.leonardwatkins182cordovatn.com</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1108 Versilia, 182, Cordova, TN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.leonardwatkins182cordovatn.com</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://www.rennerweismann1283libertystreetfranklin.com</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1283 Liberty Street, 1283 Liberty Street, Franklin, US</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.rennerweismann1283libertystreetfranklin.com</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://www.aprilwedding603eastbroadwaystreetprosper.com</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>603 East Broadway Street, 603 East Broadway Street, Prosper, US</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.aprilwedding603eastbroadwaystreetprosper.com</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://cascade-partners.com/team-member/stephen-weber</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Driehaus Capital Management LLC, Grand Rapids, Michigan, IL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://cascade-partners.com/team-member/stephen-weber</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://www.healthcare.gov/search/healthcare-professionals/anthony-woods-0001231919-26-000249</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>c/o Raintank Inc., San Francisco, CA, NY</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.healthcare.gov/search/healthcare-professionals/anthony-woods-0001231919-26-000249</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Robots.txt restricts crawling on https://www.healthcare.gov/search/healthcare-professionals/anthony-woods-0001231919-26-000249.; AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://www.bennettweaver20thflooratlantaga.com</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3280 Peachtree Road, 20th Floor, ATLANTA, GA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.bennettweaver20thflooratlantaga.com</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://in.investing.com/news/stock-market-news/form-def-14a-alphatec-holdings-inc-for-23-june-93CH-5465992</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>104 COOPER CT., Los Gatos, California, US</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://in.investing.com/news/stock-market-news/form-def-14a-alphatec-holdings-inc-for-23-june-93CH-5465992</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Front Office Bios - Craig Weissman</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/giants/team/front-office/craig-weissman</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>+12026756287, +12063464000, +12154636000, +12164204200, +13032920200, +13054801300, +13126741000, +13134712000, +13143459600, +14046142300, +14106859800, +14123235000, +14149024400, +14159722000, +14163411000, +15137657000, +16024626500, +16126593400, +16172679440, +16197955000, +17132598000, +17149402000, +17182934300, +17185076387, +17278253137, +17734042827, +18169218000, +18175331972</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>90 NEW MONTGOMERY ST., La Costa, California, CA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.mlb.com/giants/team/front-office/craig-weissman, https://www.mlb.com/team, https://www.mlb.com/giants/history</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>VirtuAlly</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://solventnetworks.com/endorsed_partners/virtually</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>jwechsler@virtually.io</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>+18034546959</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>c/o BLV Manager LLC, Charleston, South Carolina, MA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://solventnetworks.com/endorsed_partners/virtually</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/solvent-networks/</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCYC0uUIgNlXgqv3Opjtvc-Q</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://www.toyotaoflincoln.com/about-us/staff</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>8 The Green, Lincoln, Nebraska, DE</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.toyotaoflincoln.com/about-us/staff</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Finding work for executives lays foundation for success</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://www.reviewjournal.com/business/finding-work-for-executives-lays-foundation-for-success</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>hstutz@reviewjournal.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>+17024773871</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1697 Northbluff Road, Las Vegas, NV, US</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.reviewjournal.com/business/finding-work-for-executives-lays-foundation-for-success</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reviewjournal</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reviewjournal/</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://twitter.com/reviewjournal</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCKk6TkLfOoXs2T4vfvdGlnw</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://www.dwebblaw.com/contact</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3811 Turtle Creek Blvd, Little Rock, Arkansas, TX</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.dwebblaw.com/contact</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Our People</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://www.weikinvest.com/our-people.htm</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>advisor@albright.sarah, info@weikinvest.com, sorority@albright.she</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>+16103762240</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>18 Commerce Drive, Wyomissing, PA, US</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.weikinvest.com/our-people.htm</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sam Wegenke</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://o2investment.com/team-member/sam-wegenke</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>swegenke@o2investment.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>+12485544239</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>40900 Woodward Ave, Bloomfield Hills, Michigan, MI</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://o2investment.com/team-member/sam-wegenke</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>About Inside Self-Storage</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://www.insideselfstorage.com/author/steven-wear</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>+12127107424, +18002621954</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3023 N Clark St., Chicago, IL, IL</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.insideselfstorage.com/author/steven-wear, https://www.insideselfstorage.com/about-inside-self-storage, https://www.insideselfstorage.com/iss-brand/video-seminar-darren-kelley-of-right-move-storage-helps-you-improve-your-self-storage-ancillary-revenue, https://www.insideselfstorage.com/author/iss-staff</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/inside-self-storage</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/InsideSelfStorage/</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/insideselfstorage/</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://twitter.com/SelfStorage_ISS</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://katieweiler.dr-leonardo.com/locations.html</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>+14422440019</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>68 Commercial Street, Carlsbad, CA, US</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://katieweiler.dr-leonardo.com/locations.html, https://katieweiler.dr-leonardo.com/locations.html, https://katieweiler.dr-leonardo.com/about-us.html, https://katieweiler.dr-leonardo.com/contact</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://seercap.com</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1177 Avenue of the Americas, New York, New York, NY</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://seercap.com</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://lawyers.findlaw.com/connecticut/bridgeport/2638434_1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Cedarview Capital Management, Bridgeport, CT, NY</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://lawyers.findlaw.com/connecticut/bridgeport/2638434_1</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://www.mto.com/lawyer/jeffrey-i-weinberger</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>9700 East 146th Street, Los Angeles, CA, IN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.mto.com/lawyer/jeffrey-i-weinberger</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Justin Webb, Speaker</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://getapeptalk.com/experts/justin-webb-speaker</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>audience@scale.fees, experts@getapeptalk.com, hello@getapeptalk.com, justin.webb@getapeptalk.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>+17378885112, +442038352929</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2407 Park Drive, London, United Kingdom, PA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://getapeptalk.com/experts/justin-webb-speaker</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/getapeptalk/</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/getapeptalk/</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@getapeptalk</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Contact — Stonecrest Partners</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://www.stonecrestpartners.com/contact-1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>djones@stonecrestpartners.com, jrandolph@stonecrestpartners.com, rprann@stonecrestpartners.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>+12012584756, +13056779595, +17876800999, +18663421069</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1369 Ashford Ave, San Juan, PR, PR</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.stonecrestpartners.com/contact-1</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://www.birminghammail.co.uk/news/local-news/nigel-wood-birmingham-mail-2060114</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>40 Gracechurch Street, Birmingham, Alabama, US</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.birminghammail.co.uk/news/local-news/nigel-wood-birmingham-mail-2060114</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>RPM Ventures</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://www.rpmvc.com/team</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>320 North Main Street, Ann Arbor, Michigan, MI</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.rpmvc.com/team, https://www.rpmvc.com/team, https://www.rpmvc.com/contact, https://www.rpmvc.com/contact-us</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adamboyden/</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://twitter.com/rpmvc</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://www.streetinsider.com/SEC+Filings/Form+D+Hometown+Pet+Holdings%2C/25856216.html</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2 Alhambra Street, San Francisco, California, CA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.streetinsider.com/SEC+Filings/Form+D+Hometown+Pet+Holdings%2C/25856216.html</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Wealth Advisors Feeder Fund I LP</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://aum13f.com/fund/wealth-advisors-feeder-fund-i-lp</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>tony@aum13f.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>+13125956000</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>353 North Clark Street, Chicago, Illinois, US</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://aum13f.com/fund/wealth-advisors-feeder-fund-i-lp</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Proprietary Trading and Investment Advisory Firm</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://tradelinkllc.com</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>+13122642000, +13122642001, +17866296660, +17866297441, +442076189200</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Tradelink Capital LLC, Chicago, Illinois, IL</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://tradelinkllc.com, https://tradelinkllc.com/about-us/, https://tradelinkllc.com/contact, https://tradelinkllc.com/contact-us</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Noah Waxman</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://noahwaxman.com/pages/contact</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>free@checkout.shippi, purchase@checkout.once, shop@noahwaxman.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>335 Madison Avenue, New York, NY, NY</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://noahwaxman.com/pages/contact, https://noahwaxman.com/pages/contact, https://noahwaxman.com/pages/contact#MainContent, https://noahwaxman.com/apps/help-center</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://facebook.com/NoahWaxmanUSA</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>http://instagram.com/NoahWaxmanUSA</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://www.wdcprojectcomanagerllcsuite108raleighnc.com</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>8045 Arco Corporate Drive, Suite 108, Raleigh, NC</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.wdcprojectcomanagerllcsuite108raleighnc.com</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://quadreal.com/about-us/our-leadership</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>c/o QuadReal Property Group, New York City, United States, A1</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://quadreal.com/about-us/our-leadership</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Contact — Adam Watts</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>http://www.adamwattsofficial.com/contact</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>adamwattsmusic@gmail.com, now@www.myartisttype.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>224 Fossil Hills Loop, Nashville, Tennessee, US</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>http://www.adamwattsofficial.com/contact, http://www.adamwattsofficial.com/contact, http://www.adamwattsofficial.com/contact#header, http://www.adamwattsofficial.com/about</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>http://instagram.com/adamwattsmusic</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Advertising execs: Stand by your word and provide the wow factor</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://vegasinc.lasvegassun.com/business/2016/dec/26/advertising-execs-stand-by-your-word-and-provide-t</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>4245 S. Grand Canyon Dr., Las Vegas, Nevada, NV</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://vegasinc.lasvegassun.com/business/2016/dec/26/advertising-execs-stand-by-your-word-and-provide-t, https://vegasinc.lasvegassun.com/about/, https://vegasinc.lasvegassun.com/staff/vegas-inc-staff/</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://fconline.foundationcenter.org/fdo-grantmaker-profile</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1350 Broadway, Tenafly, NJ, NY</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://fconline.foundationcenter.org/fdo-grantmaker-profile</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://www.towerbrook.com/our-team/walter-weil</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>733 Third Avenue, New York, NY, US</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.towerbrook.com/our-team/walter-weil</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>IAPD</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/individual/summary/4011917</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>718 Washington Ave N, Springfield, MO, MN</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/individual/summary/4011917, https://adviserinfo.sec.gov/contact, https://adviserinfo.sec.gov/contact-us, https://adviserinfo.sec.gov/about</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://www.wavertonmanagerllcsuite210developmentbranchesva.com</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>5131 RIVER CLUB DR, SUITE 210, development branches, VA</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.wavertonmanagerllcsuite210developmentbranchesva.com</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://www.michaelwatts2108draytonstreetsavannah.com</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2108 DRAYTON STREET, 2108 DRAYTON STREET, Savannah, US</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.michaelwatts2108draytonstreetsavannah.com</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://www.marinowayne5thfloornewyorkny.com</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Stripes, 5th Floor, New York, NY</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.marinowayne5thfloornewyorkny.com</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WCM PARTNERS X, LLC</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://whalewisdom.com/filer/wcm-partners-x-llc-series-x1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>contact@whalewisdom.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>281 Brooks Street, Laguna Beach, CA, US</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://whalewisdom.com/filer/wcm-partners-x-llc-series-x1, https://whalewisdom.com/contact, https://whalewisdom.com/whitepapers/whalewisdom, https://whalewisdom.com/about</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/whalewisdom13f/</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>https://twitter.com/whalewisdom</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://www.johnwatsonpobox187evergreen.com</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>P. O. Box 187, P. O. Box 187, Evergreen, US</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.johnwatsonpobox187evergreen.com</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Billy Webster - Advance America Cash Advance Centers Inc. - Biography</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://www.legistorm.com/person/bio/96131/William_Mendenhall_Webster_IV.html</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>congress@legistorm.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>+12023604172</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>200 Park Avenue, Spartanburg, SC, NY</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.legistorm.com/person/bio/96131/William_Mendenhall_Webster_IV.html</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>https://twitter.com/LegiStorm</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://www.vincentweisser.com/imprint</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>c/o Prime Intellect, Dover, Delaware, DE</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.vincentweisser.com/imprint, https://www.vincentweisser.com/, https://www.vincentweisser.com/contact, https://www.vincentweisser.com/contact-us</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>https://twitter.com/vincentweisser</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Phil Weissbrod, MD</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://ige.ucsd.edu/node/643</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ige@ucsd.edu, pweissbrod@health.ucsd.edu</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>+18588221142</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2010 JIMMY DURANTE BLVD STE 200, San Diego, California, US</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://ige.ucsd.edu/node/643</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/igeucsandiego/</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/igeucsd</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ucsd_ige/</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>https://twitter.com/ige_ucsd</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Cambridge CEO Amy Webber Named InvestmentNews CEO of the Year</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://www.joincambridge.com/about-cambridge/news/cambridge-ceo-amy-webber-named-investmentnews-ceo-of-the-year</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>jeff.wulf@cir2.com, more@joincambridge.com.about, publicrelations@cir2.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>+18007776080, +18776882369</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1776 Pleasant Plain Rd., Fairfield, Iowa, US</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.joincambridge.com/about-cambridge/news/cambridge-ceo-amy-webber-named-investmentnews-ceo-of-the-year</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cambridge-investment-research</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CambridgeInvestmentResearch</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cambridge.investment.research/?hl=en</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>https://twitter.com/CambridgeIBD</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/CambridgeInvestmentResearchInc</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>NPPES NPI Registry</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://npiregistry.cms.hhs.gov/registry</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>c/o Intus Care Inc., Nashville, TN, RI</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://npiregistry.cms.hhs.gov/registry, https://npiregistry.cms.hhs.gov/contact, https://npiregistry.cms.hhs.gov/contact-us, https://npiregistry.cms.hhs.gov/about</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://www.normanwebbiiisuite210portsmouthnh.com</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>145 Maplewood Avenue, Suite 210, Portsmouth, NH</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.normanwebbiiisuite210portsmouthnh.com</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://www.healthgrades.com/physician/dr-suyu-zhang-ynk6</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>224 S. MICHIGAN AVENUE, New York, NY, IL</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.healthgrades.com/physician/dr-suyu-zhang-ynk6</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://www.webberwillisventuresllc15030venturablvdshermanoaks.com</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>15030 Ventura blvd, 15030 Ventura blvd, Sherman Oaks, US</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.webberwillisventuresllc15030venturablvdshermanoaks.com</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Syncracy Capital</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://www.syncracy.io</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>operations@syncracy.io</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>99 Hudson Street, New York, NY, NY</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://www.syncracy.io, https://www.syncracy.io/contact, https://www.syncracy.io/contact-us, https://www.syncracy.io/about</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Deal 3 Capital</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://deal3capital.com</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>growth@all.this, in-house@acquisition.stabil, investors@deal3capital.com, portal@deal3capital.cashflowportal.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>58 Kiva PL, 58 Kiva PL, Sandia Park, US</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://deal3capital.com, https://deal3capital.com#contact, https://deal3capital.com#about, https://deal3capital.com#team</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PathNorth</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://www.pathnorth.com/brock-weatherup</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>cmoore@pathnorth.com, dar@coachdar.com, dholladay@pathnorth.com, eddy@liftorlando.com, jkijumba@pathnorth.com, jpalalay@pathnorth.com, mhorsford@pathnorth.com, rick@rickstevenson.com, skwiecien@pathnorth.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>7945 Morningside Drive, Stonington, CT, US</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://www.pathnorth.com/brock-weatherup, https://www.pathnorth.com/our-team, https://www.pathnorth.com/our-board, https://www.pathnorth.com/contact</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/brockweatherup/</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>http://instagram.com/pathnorth</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>https://twitter.com/PathNorth</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Erik Weir</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://smartadvisormatch.com/advisor-network/south-carolina/erik-weir-2009973</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>info@smartasset.com, profile-compliance@smartasset.com, value@all.learn</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>220 N. Main Street, Greenville, SC, SC</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://smartadvisormatch.com/advisor-network/south-carolina/erik-weir-2009973, https://smartadvisormatch.com/about, https://smartadvisormatch.com/about#contact, https://smartadvisormatch.com/data</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Colin O. Webb, II</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://corporation.mit.edu/member/colin-o-webb-ii</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>corporationoffice@mit.edu</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>+16172535614, +16172538544</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>650 California Street, Los Angeles, California, CA</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://corporation.mit.edu/member/colin-o-webb-ii, https://corporation.mit.edu/contact/, https://corporation.mit.edu/staff/, https://corporation.mit.edu/about-corporation/</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Danielle Weatherholtz, Licensed Professional Clinical Counselor, Worthington, OH, 43085</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://www.psychologytoday.com/us/therapists/danielle-weatherholtz-worthington-oh/1679700</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>accessibility@psychologytoday.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>+13802142964, +16469564495</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1952 Howell Mill Rd, Worthington, Ohio, GA</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://www.psychologytoday.com/us/therapists/danielle-weatherholtz-worthington-oh/1679700, https://www.psychologytoday.com/us/groups, https://www.psychologytoday.com/about, https://www.psychologytoday.com/us/accessibility-help</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/completed_contacts.xlsx
+++ b/data/export/completed_contacts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P82"/>
+  <dimension ref="A1:P225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -439,9 +439,9 @@
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
-    <col width="38" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
     <col width="50" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
     <col width="50" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
   </cols>
@@ -924,23 +924,27 @@
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+12798000000</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2345 E. 3rd Avenue, Denver, Colorado, CO</t>
+          <t>56 Wareham Street, Boston, MASSACHUSETTS, MA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Merged</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.nasaaefd.org/FormD/primaryDocument</t>
+          <t>https://reports.adviserinfo.sec.gov/reports/ADV/315640/PDF/315640.pdf, https://reports.adviserinfo.sec.gov/contact-us, https://reports.adviserinfo.sec.gov/contact, https://reports.adviserinfo.sec.gov/about, https://www.nasaaefd.org/FormD/primaryDocument</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -949,10 +953,14 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+          <t>{"business_name": "scraper", "emails": "", "phones": ",scraper", "address": "importer"}</t>
         </is>
       </c>
     </row>
@@ -4632,6 +4640,7034 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://knighthead.com/profile</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1405 Carlotta Ln, New York, New York, US</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://knighthead.com/profile</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://muckrack.com/payton-walker</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>693 SE Glenwood Dr., Huntsville, Alabama, OR</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://muckrack.com/payton-walker</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://wallacehart.com/contact</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1792 ALYSHEBA WAY, Lexington, Kentucky, KY</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Merged</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://wallacehart.com/contact</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Verifying your browser. Please wait a few seconds...</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://www.pag.com/en/about</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>24/F, Hong Kong, Hong Kong, K3</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://www.pag.com/en/about, https://www.pag.com/contact, https://www.pag.com/contact-us, https://www.pag.com/about</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://www.hospitalitynet.org/appointment/79023123/jonathan-wachter</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>119 Braintree St., New York, New York, MA</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.hospitalitynet.org/appointment/79023123/jonathan-wachter</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>American Family Insurance, Patrick Wall Agency, Inc</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://www.westminsterchamber.biz/list/member/american-family-insurance-patrick-wall-agency-inc-2241</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>info@westminsterchamber.biz</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>+13034269500, +13039615975, +18555448307</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>c/o BNYM Fund Services (Ireland) DAC, Northglenn, Colorado, L2</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://www.westminsterchamber.biz/list/member/american-family-insurance-patrick-wall-agency-inc-2241</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/3545807</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WestminsterCC</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Nitin R. Wadke of Bloom Tree Partners Llc</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>http://www.symmetric.io/hedge-fund-employee/NITIN-R-WADKE-18F0</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>info@symmetric-info.com, info@symmetric.io</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>+12127162615, +18662434178, +19175912970</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>420 Lexington Avenue, New York, NY, NY</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>http://www.symmetric.io/hedge-fund-employee/NITIN-R-WADKE-18F0, http://www.symmetric.io/index/about, http://www.symmetric.io/contact, http://www.symmetric.io/contact-us</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2069970/000101297525000280/xslFormDX01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>c/o Hg Pooled Management Limited, London, UNITED KINGDOM, X0</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Merged</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1774572/000177457226000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1802083/000091957420000939/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1878965/000187896523000004/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1934798/000193479826000001/xslFormDX08/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1965372/000093583624000102/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2024838/000202483824000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2032432/000119312524284215/d871783dn2a.htm, https://www.sec.gov/Archives/edgar/data/2048487/000090866224000020/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2069970/000101297525000280/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2091049/000209104926000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2099557/000209955726000002/xslFormDX01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Entrepreneur 2024</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://www.entrepreneurindia.com/ashish-wadhwani.php</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>+916354604762, +917827499785, +917838594787, +918595350505, +919217373038, +919650438744</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1510 Cohn St, Singapore, Houston, US</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://www.entrepreneurindia.com/ashish-wadhwani.php, https://www.entrepreneurindia.com/cdn-cgi/l/email-protection#80f0f2e1f4e5e5ebc0e5eef4f2e5f0f2e5eee5f5f2e1f0eaaee3efed, https://www.entrepreneurindia.com/cdn-cgi/l/email-protection#8ee5e5effde6f7effeceebe0fafcebfefcebe0ebfbfce7e0eae7efa0ede1e3, https://www.entrepreneurindia.com/cdn-cgi/l/email-protection#e595848b8e848f878d9091848b8ca5808b9197809597808b8090978c8b818c84cb868a88</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/entrepreneur-media-india/mycompany/</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/EntrepreneurInd</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/EntrepreneurIND</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>https://twitter.com/EntrepreneurIND</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@EntrepreneurIndiamedia</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Sebastian Wagner</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.corcoran.com/real-estate-agents/detail/agent/sebastian-wagner/26165</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>info@corcoran.com, sebastian.wagner@corcoran.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>+12123553550, +18005444055</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Suite 1000, Miami Beach, Florida, A1</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.corcoran.com/real-estate-agents/detail/agent/sebastian-wagner/26165</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://www.gurufocus.com/insider/281254/waldeck-george-p-jr.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>655 Broad Street, Newark, NJ, US</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://www.gurufocus.com/insider/281254/waldeck-george-p-jr.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AXCS Website</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://www.axcscapital.com/full-team/ken-vyhmeister</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>info@axcscapital.com, ken.vyhmeister@axcscapital.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>+15093015269</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>317 Commercial Avenue, 317 Commercial Avenue, Anacortes, US</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://www.axcscapital.com/full-team/ken-vyhmeister</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ekvcpa/</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/axcs.capital</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://eigpartners.com/team/randall-wade</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>600 NEW HAMPSHIRE AVE NW, Washington, DC, DC</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://eigpartners.com/team/randall-wade</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://www.bmc.org/about-us/directory/doctor/daniel-j-wallman-md</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2125 South Beverly Drive, Boston, Massachusetts, US</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://www.bmc.org/about-us/directory/doctor/daniel-j-wallman-md</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://pitchbook.com/profiles/investor/175730-14</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>152 West 57th Street, Tel Aviv, New York, NY</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Merged</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://pitchbook.com/profiles/investor/175730-14, https://pitchbook.com/profiles/investor/232480-00</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://www.mcguirewoods.com/people/w/james-c-walls</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>200 River Market Avenue, Pittsburgh, Pennsylvania, AR</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://www.mcguirewoods.com/people/w/james-c-walls</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://www.bfly.com/contact</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>+13104094994</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>9595 Wilshire Boulevard, Beverly Hills, California, CA</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://www.bfly.com/contact, https://www.bfly.com/contact, https://www.bfly.com/team, https://www.bfly.com/</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Darrick Walker</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com/profile/darrick-walker</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>corrections@forbes.com, feedback@forbes.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1912 Capitol Avenue, Walnut Creek, California, WY</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com/profile/darrick-walker, https://www.forbes.com/contact/, https://www.forbes.com/vetted/home-office/, https://www.forbes.com/fdc/contact.html</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dialog/feed?app_id=123694841080850&amp;link=https%3A%2F%2Fwww.forbes.com%2Fsites%2Fmolly-bennard%2F2026%2F07%2F09%2Fmethodology-2026-forbes--shook-top-financial-security-professionals%2F&amp;picture=https%3A%2F%2Fimageio.forbes.com%2Fspecials-images%2Fimageserve%2F6a515bc73c8b1cd3f0dba519%2F0x0.jpg%3Fformat%3Djpg%26width%3D440&amp;name=Methodology%3A%202026%20Forbes%20%7C%20Shook%20Top%20Financial%20Security%20Professionals&amp;caption=www.forbes.com&amp;description=The%20annual%20Forbes%20%7C%20SHOOK%20ranking%20of%C2%A0%20Top%20Financial%20Security%20Professionals%20(FSPs)%20identifies%20those%20professionals%20who%20specialize%20in%20life%20insurance%20and%20annuities%20and%20whom%20families%20rely%20on%20for%20wealth%20planning%20and%20protection.%20Extensive%20research%20is%20conducted%20by%20SHOOK%20Research.</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://news.prudential.com/us-en/company-info/leadership</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>751 Broad Street, Newark, New Jersey, US</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://news.prudential.com/us-en/company-info/leadership, https://news.prudential.com/us-en/contact-us, https://news.prudential.com/us-en/company-info/leadership, https://news.prudential.com/us-en/research-and-commentary/thought-leadership</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://www.corywakesuite2200norfolkva.com</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>440 Monticello Avenue, Suite 2200, Norfolk, VA</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://www.corywakesuite2200norfolkva.com</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Staff Directory • St. James Parish, LA • CivicEngage</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://www.stjamesla.com/directory.aspx</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>+12252652409, +12252659066, +12255622200, +12255622260, +12255622266, +12255622285, +12255622293, +12255622295, +12255622304, +12255622337, +12255622364, +12255622400, +12255622419, +12255622431, +12255622470, +12255622500, +12255622525, +12255622910, +12255623767, +12255627855, +12258693618, +12258694747, +12258698067, +12258698298</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>3131 N. 1-10 Service Rd. E., Convent, LA, US</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://www.stjamesla.com/directory.aspx, https://www.stjamesla.com/Directory.aspx?did=67, https://www.stjamesla.com/Directory.aspx?did=9, https://www.stjamesla.com/Directory.aspx?did=38</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Cyrus Wadia</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://activate.org/cyrus-wadia-ceo</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>c/o Mechanical Orchard, 36th Floor, San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://activate.org/cyrus-wadia-ceo, https://activate.org/contact, https://activate.org/about-us, https://activate.org/team</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cyruswadia/</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/activatefellows/</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>https://x.com/activatefellows</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@activatefellows</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://theiwagroup.com/joyce-ann-wainaina</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>theiwagroup@outlook.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Kofisi #713 Block 1, Nairobi, Nairobi, M3</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://theiwagroup.com/joyce-ann-wainaina, https://theiwagroup.com/contact, https://theiwagroup.com/office-politics-for-the-pure-in-heart/, https://theiwagroup.com/about-iwa</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Christ Church Episcopal School</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://projects.propublica.org/nonprofits/organizations/571122062</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>245 Cavalier Drive, Greenville, South Carolina, US</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://projects.propublica.org/nonprofits/organizations/571122062, https://projects.propublica.org/nonprofits/contact, https://projects.propublica.org/contact, https://projects.propublica.org/contact-us</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>https://github.com/betson/irs-efile-viewer</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://www.jeannievusuite903sanjuanpr.com</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>53 Calle Las Palmeras, Suite 903, San Juan, PR</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://www.jeannievusuite903sanjuanpr.com</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://www.davewaisersuite99105miamifl.com</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>382 NE 191st Street, Suite 99105, Miami, FL</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://www.davewaisersuite99105miamifl.com</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://www.jameswalkersuite2700chicagoil.com</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>One North Wacker Drive, Suite 2700, Chicago, IL</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://www.jameswalkersuite2700chicagoil.com</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://www.victorvonklemperersuite401ospreyfl.com</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>644 Fernwalk Lane, Suite 401, Osprey, FL</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://www.victorvonklemperersuite401ospreyfl.com</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://gracewalker-ca.webflow.io/info</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>hello@gracewalker.ca</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>C/O DOUBLELINE FUNDS, Calgary, Alberta, FL</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://gracewalker-ca.webflow.io/info, https://gracewalker-ca.webflow.io/contact, https://gracewalker-ca.webflow.io/contact-us, https://gracewalker-ca.webflow.io/about</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/walkergrace/</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/graceongrid/</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://digileaders.com/wp-content/uploads/2023/09/Cyber-report-2023.pdf</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>dan@dkclarkephoto.com, p@3aylb.uhc, p@f.brb, task@office.copy</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>+13104959</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>200 W. Martin Luther King Blvd., London, Chattanooga, TN</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://digileaders.com/wp-content/uploads/2023/09/Cyber-report-2023.pdf</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: All providers failed for structured query. Last error: Gemini rate limited (429). Retry after 60.0s.</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://www.brianwallick730thirdavenuenewyork.com</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>730 Third Avenue, 730 Third Avenue, New York, US</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://www.brianwallick730thirdavenuenewyork.com</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Sadek_Wahba</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>c/o I Squared Capital Advisors (US) LLC, Miami, FL, FL</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Merged</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Portal_Space_Systems, https://en.wikipedia.org/wiki/Sadek_Wahba</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Dawn Walloch, Principal at Platinum Equity</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://www.platinumequity.com/people/dawn-walloch</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>+12035350899, +12039302010, +12129050010, +13102829202, +13107121850, +17814618888, +442035350899, +6567094090</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>360 North Crescent Drive, Los Angeles, California, CA</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://www.platinumequity.com/people/dawn-walloch, https://www.platinumequity.com/contact-us/, javscript:;, https://www.platinumequity.com/about-us/</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/platinum-equity</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>https://twitter.com/PlatinumEquity</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>HTTP subpage failed: javscript:; - Failed after 0 attempts. Last error: Unexpected error: unknown url type: '/;'; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Thomas R Wall</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://kando.tech/person/thomas-r-wall</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Kelso &amp; Company, New York, NY, NY</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://kando.tech/person/thomas-r-wall, https://kando.tech/help, https://kando.tech/contact/feedback, https://kando.tech/company/kando-technologies-inc</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/67949094/</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>https://twitter.com/kandotech</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://reports.adviserinfo.sec.gov/reports/ADV/107235/PDF/107235.pdf</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>p9@-.gc</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>+13276800000</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>230 Park Avenue, New York, New York, NY</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Merged</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://reports.adviserinfo.sec.gov/about, https://reports.adviserinfo.sec.gov/contact, https://reports.adviserinfo.sec.gov/contact-us, https://reports.adviserinfo.sec.gov/reports/ADV/107235/PDF/107235.pdf, https://reports.adviserinfo.sec.gov/reports/ADV/304706/PDF/304706.pdf</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": ",scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>PACT Capital Partners</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://tracxn.com/d/private-equity/pactcapitalpartners/__zRzBnHTMSi-spFglOWTy3ucWnk8wtF05I6bK5jJesfg</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>hi@tracxn.com</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>+919939090919</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>330 MADISON AVENUE, New York, NY, NY</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://tracxn.com/d/private-equity/pactcapitalpartners/__zRzBnHTMSi-spFglOWTy3ucWnk8wtF05I6bK5jJesfg</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Robots.txt restricts crawling on https://tracxn.com/d/private-equity/pactcapitalpartners/__zRzBnHTMSi-spFglOWTy3ucWnk8wtF05I6bK5jJesfg.</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://www.dailyherald.com/20220814/business/coffee-break-getting-to-know-tim-walbert-chairman-president-and-ceo-of-horizon-therapeutics</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>c/o Mirum Pharmaceuticals, Deerfield, IL, CA</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://www.dailyherald.com/20220814/business/coffee-break-getting-to-know-tim-walbert-chairman-president-and-ceo-of-horizon-therapeutics, https://www.dailyherald.com/contact, https://www.dailyherald.com/contact-us, https://www.dailyherald.com/about</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://pubs.acs.org/doi/10.1021/acs.jcim.7b00403</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>250 SUTTER ST. SUITE 650, San Francisco, California, US</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://pubs.acs.org/doi/10.1021/acs.jcim.7b00403</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://business.uq.edu.au/profile/19097/kim-vu</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>c/o Spring Education Group, Brisbane, Queensland, CA</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://business.uq.edu.au/profile/19097/kim-vu</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://www.dbag.com/fileadmin/documents/team/board/CV_AR_vonHodenberg_eng_s.pdf</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>mobility@pricewaterhousecoopers.brigit, stimmrechte@dbag.de, welcome@dbag.de</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>+49699578701, +496995787199, +496995787270, +496995787293, +496995787296, +496995787363</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Glusingen 2, Hamburg, Betzendorf, 2M</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://www.dbag.com/fileadmin/documents/team/board/CV_AR_vonHodenberg_eng_s.pdf, https://www.dbag.com/contact, https://www.dbag.com/contact-us, https://www.dbag.com/about</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/deutsche-beteiligungs-ag/mycompany/verification/?viewAsMember=true</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Mulford Waldrop — Mortgage Loan Officer in Columbus, GA</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://www.experience.com/reviews/mulford-13343740</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>+17065965195</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>6551 Green Island Drive, Columbus, Georgia, GA</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://www.experience.com/reviews/mulford-13343740, https://www.experience.com/request-a-demo, https://www.experience.com/contact, https://www.experience.com/contact-us</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/experiencecom/</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/experiencecom</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/experience_com/</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>https://x.com/experience__com</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@experience_com</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://www.niagaracounty.gov/Instructors%20-%20Safety%20Course%203_21_25.pdf</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>c/o Maritime Capital LLC, Youngstown, New York, NY</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://www.niagaracounty.gov/Instructors%20-%20Safety%20Course%203_21_25.pdf</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://kin.sfsu.edu/people/david-walsh</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>6363 S. FIDDLERS GREEN CIRCLE, San Francisco, California, CO</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://kin.sfsu.edu/people/david-walsh</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>FERNS</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://ferns.odf.oregon.gov/E-Notification/noap/136971</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>joe.l.goldsby@oregon.gov</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>+13606409591, +15034670829, +15038292216, +16296050150, +16296050170</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>721 NW 9th Avenue, Portland, OR, OR</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://ferns.odf.oregon.gov/E-Notification/noap/136971</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Simon von Oppenheim - 747 Capital</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://informaconnect.com/superreturn-family-office-europe/speakers/simon-von-oppenheim</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>lee.granville@informa.com, lpsuperreturneurope@informa.com, rachel.lewis@informa.com, sam.fullalove@informa.com, sponsorsuperreturn@informa.com, stephen.ashiotis@informa.com, worked@sal.oppenh</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>+447385005011, +447721102019, +447867441118, +447990007530</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>c/o 747 Capital LLC, 17th Floor, Switzerland, NY</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://informaconnect.com/superreturn-family-office-europe/speakers/simon-von-oppenheim, https://informaconnect.com/superreturn-family-office-europe/contact/, https://informaconnect.com/superreturn-family-office-europe/, https://informaconnect.com/superreturn-family-office-europe/agenda/</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/SRFOEurope/</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCWkO2zFvz3WJ4y3q9dsKOwQ/</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Staff Directory • City of Webster Groves • CivicEngage</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://webstergrovesmo.gov/directory.aspx</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>+13146453000, +13149635300, +13149635302, +13149635303, +13149635305, +13149635313, +13149635315, +13149635318, +13149635319, +13149635331, +13149635345, +13149635402, +13149635416, +13149635432, +13149635600, +13149637561</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>5525 N. MACARTHUR BLVD., Webster Groves, Missouri, TX</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://webstergrovesmo.gov/directory.aspx, https://webstergrovesmo.gov/Directory.aspx?did=73, https://webstergrovesmo.gov/directory.aspx, https://webstergrovesmo.gov/contact</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/webstergrovescity/</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@cityofwebstergroves9068</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://www.johnwalsh4000ericssondrivewarrendale.com</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>4000 Ericsson Drive, 4000 Ericsson Drive, Warrendale, US</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://www.johnwalsh4000ericssondrivewarrendale.com</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://www.michaelvranossuite301oldgreenwichct.com</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>c/o E/S MBS GP I LLC, Suite 301, Old Greenwich, CT</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://www.michaelvranossuite301oldgreenwichct.com</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>EdgeMode</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://www.edgemode.io/contact</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>development@manage.com</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>110 E. BROWARD BLVD. SUITE 1700, Fort Lauderdale, Florida, US</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://www.edgemode.io/contact, https://www.edgemode.io/contact, https://www.edgemode.io/contact-us, https://www.edgemode.io/about</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Walker &amp; Dunlop Investment Partners</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://www.walkerdunlop.com/services/investment-management/investment-partners</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>info@walkerdunlop.com, wdip@walkerdunlop.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>+13012155500</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2345 E. 3rd Avenue, Suite 300, Denver, CO</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://www.walkerdunlop.com/services/investment-management/investment-partners</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/walker-&amp;-dunlop/</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WalkerDunlop/</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/walkerdunlop/</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>https://twitter.com/walkerdunlop/</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC5jhzGBWOTvQku2kLbucGcw</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://www.atiawalid5federalstbellerica.com</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>5 Federal St, 5 Federal St, Bellerica, US</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://www.atiawalid5federalstbellerica.com</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://www.manasivydyanath169madisonaveste11524newyork.com</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>169 Madison Ave STE 11524, 169 Madison Ave STE 11524, New York, US</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://www.manasivydyanath169madisonaveste11524newyork.com</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://www.michaelwall507725marinedrivenorthvancouver.com</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>507-725 Marine Drive, 507-725 Marine Drive, North Vancouver, US</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://www.michaelwall507725marinedrivenorthvancouver.com</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>https://www.tuomovuolteenaho109e17thstreetcheyenne.com</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>109 E 17TH STREET, 109 E 17TH STREET, CHEYENNE, US</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://www.tuomovuolteenaho109e17thstreetcheyenne.com</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>https://www.samw16thfloornewyorkny.com</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>100 Avenue of the Americas, 16th Floor, New York, NY</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://www.samw16thfloornewyorkny.com</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>https://www.charlottewalker1stfloorstheliery9.com</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>5-6 Esplanade, 1st Floor, St. Helier, Y9</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://www.charlottewalker1stfloorstheliery9.com</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>https://www.gurdevanwalia1238beverlyhillsca.com</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>369 S. Doheny Drive, #1238, Beverly Hills, CA</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://www.gurdevanwalia1238beverlyhillsca.com</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>https://www.marywagerpobox840mercerislandwa.com</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>7432 SE 71st Street, PO Box 840, Mercer Island, WA</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://www.marywagerpobox840mercerislandwa.com</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>https://www.voyagerpartnersgpllcsuite800dallastx.com</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>16000 Dallas Parkway, Suite 800, Dallas, TX</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://www.voyagerpartnersgpllcsuite800dallastx.com</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>https://www.johnwadejr750lexingtonavenuenewyork.com</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>750 Lexington Avenue, 750 Lexington Avenue, New York, US</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://www.johnwadejr750lexingtonavenuenewyork.com</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://www.davidwalker136sheddenrdgrandcaymane9.com</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>350 South Sound Road, 136 Shedden Rd, Grand Cayman, E9</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://www.davidwalker136sheddenrdgrandcaymane9.com</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>https://www.andreavossler50fountainplazabuffalo.com</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>50 Fountain Plaza, 50 Fountain Plaza, Buffalo, US</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://www.andreavossler50fountainplazabuffalo.com</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Russ Walker</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>https://www.slatesells.com/agents/russ-walker</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>russ@slatesells.com</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>+13178550216, +13179656106</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>13240 S Sunset Stream Way, Fishers, IN, US</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://www.slatesells.com/agents/russ-walker</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>https://www.walnutcreeklbgpllcsuite315houstontx.com</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>5373 West Alabama, Suite 315, Houston, TX</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://www.walnutcreeklbgpllcsuite315houstontx.com</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Wagner Johnson Productions</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>https://www.wagnerjohnson.com/contact</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>+12124333024</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>130 W 42nd Street, New York, New York, NY</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://www.wagnerjohnson.com/contact, https://www.wagnerjohnson.com/contact#page, https://www.wagnerjohnson.com/contact, https://www.wagnerjohnson.com/about</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wjplive</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wjplive</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wjplive</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>https://twitter.com/wjplive</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>https://lawyers.justia.com/lawyer/christina-marie-von-poelnitz-1631252</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>1001 Pennsylvania Avenue, New York, New York, DC</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://lawyers.justia.com/lawyer/christina-marie-von-poelnitz-1631252</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>https://www.denniswallacefloor31newyorkny.com</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>780 3rd Avenue, Floor 31, New York, NY</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://www.denniswallacefloor31newyorkny.com</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>https://www.loopnet.com/commercial-real-estate-brokers/profile/timothy-wallen/hgcpzd0b</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>19000 W. Bluemound Rd., Brookfield, Wisconsin, US</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://www.loopnet.com/commercial-real-estate-brokers/profile/timothy-wallen/hgcpzd0b</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>https://magcp.com/team</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>4020 Maple Avenue, San Francisco, California, TX</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://magcp.com/team</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>https://www.johnwallingtonsuite220boulderco.com</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2955 Valmont Road, Suite 220, Boulder, CO</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://www.johnwallingtonsuite220boulderco.com</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>https://www.josephvotelsuite650arlingtonva.com</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>241 18th Street South, Suite 650, Arlington, VA</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://www.josephvotelsuite650arlingtonva.com</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>IAPD</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/135434</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>12400 Wilshire Blvd, Los Angeles, California, CA</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/135434, https://adviserinfo.sec.gov/contact, https://adviserinfo.sec.gov/contact-us, https://adviserinfo.sec.gov/about</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://www.wailescapital.com/team</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>a@accenture.garris, garrison@wailescapital.com, info@mysite.com, info@wailescapital.com</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>5502 Zoemark Lane, Houston, Texas, US</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://www.wailescapital.com/team, https://www.wailescapital.com/contact-8, https://www.wailescapital.com/team, https://www.wailescapital.com/who-we-are</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/garrison-jones-6a41165a/</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Dr. Timothy Wall - School of Education</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>https://www.nwmissouri.edu/education/directory/wall.htm</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>timwall@nwmissouri.edu</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>+16605621179, +16605621561</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>50 Lakeside Avenue, Maryville, MO, US</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://www.nwmissouri.edu/education/directory/wall.htm</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/nwmissouri</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nwmostate/</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>https://www.twitter.com/nwmostate</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/NorthwestVideo</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Event's Details</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>https://pranichealing.com/event/details/6663</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>meeta@pranichealing.com</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>+19259630293</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>1 Controls Drive, Pleasanton, California, US</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://pranichealing.com/event/details/6663</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PranicHealingOnline/</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pranichealing_com</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/masterstephenco</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>John Charles Wain, MD - Dana-Farber Cancer Institute</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>https://www.dana-farber.org/find-a-doctor/john-charles-wain</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>surgery@st.elizab</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>+16176323000, +16176325301, +16176325786, +18774413324, +18887334662</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2121 Avenue of the Stars, Boston, MA, CA</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://www.dana-farber.org/find-a-doctor/john-charles-wain</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dana-farber-cancer-institute</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/danafarbercancerinstitute</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>https://instagram.com/danafarber</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>https://twitter.com/danafarber</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/DanaFarberCancerInst</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>A-Waldron-Electric-Heating-Cooling</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/agencies/dli/programs-services/labor-management-relations/bureau-of-occupational-and-industrial-safety/tpa-buildings/a-waldron-electric-heating-cooling</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>admin@equalemployment.org, wcoaresourcecenter@pa.gov</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>+12155577112, +12155577602, +14123842931, +17174257758, +17177723702, +17177724447, +17177724991, +18003250778, +18003624228, +18004822383, +18007721213, +18442376316, +18887452357, +18887721409</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>111 Goodhill Road, Pittsburgh, Pennsylvania, US</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://www.pa.gov/agencies/dli/programs-services/labor-management-relations/bureau-of-occupational-and-industrial-safety/tpa-buildings/a-waldron-electric-heating-cooling, https://www.pa.gov/agencies/dli/programs-services/workers-compensation/workers-compensation-office-of-adjudication-wcoa, https://www.pa.gov/agencies/dli/resources/forms-and-documents/office-of-vocational-rehabilitation, https://www.pa.gov/agencies/dli/departments-offices/health-and-disabilities/office-of-disability-determination</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GovernorShapiro</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/GovernorShapiro/</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>https://x.com/GovernorShapiro</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@GovernorShapiro</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>https://www.blairwallace26thfloornewyorkny.com</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>437 Madison Avenue, 26th Floor, New York, NY</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://www.blairwallace26thfloornewyorkny.com</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>https://www.henrywagner253sanfranciscoca.com</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>12269 Chestnut Street, #253, San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://www.henrywagner253sanfranciscoca.com</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Nuvaira has filed a notice of an exempt offering of securities to raise $63,576,279.00 in New Funding.</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>https://www.intelligence360.news/nuvaira-has-filed-a-notice-of-an-exempt-offering-of-securities-to-raise-63576279-00-in-new-funding</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>online@www.intelligence360.io</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>+17634502800, +18008496058</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>6500 Wedgwood Road North, Minneapolis, Minnesota, MN</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://www.intelligence360.news/nuvaira-has-filed-a-notice-of-an-exempt-offering-of-securities-to-raise-63576279-00-in-new-funding, https://www.intelligence360.news/contact-us/, https://www.intelligence360.news/about-us/, https://www.intelligence360.news/contact</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nuvaira-inc./</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel//</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>https://www.davidvoorhes28drtonysrdkatonah.com</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>28 Dr. Tonys Rd., 28 Dr. Tonys Rd., Katonah, US</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://www.davidvoorhes28drtonysrdkatonah.com</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>https://www.thomasvoutsosste7235toledooh.com</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>3550 Executive Pkwy, Ste 7235, Toledo, OH</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://www.thomasvoutsosste7235toledooh.com</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>https://www.haleywaldronsuite1800dallastx.com</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2300 N. FIELD STREET, SUITE 1800, Dallas, TX</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://www.haleywaldronsuite1800dallastx.com</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>https://www.suewagnersuite1401newyorkny.com</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>c/o Wagner Johnson Productions LLC, Suite 1401, New York, NY</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://www.suewagnersuite1401newyorkny.com</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Veteran Ventures Capital</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>https://www.privateequityinternational.com/institution-profiles/veteran-ventures-capital.html</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>alistair.r@peimedia.com, customerservices@peimedia.com, inquiry@veteranventures.us, researchandanalytics@peimedia.com, subscriptions@pei.group, subscriptions@peimedia.com</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>1640 Boro Pl, McLean, Virginia, VA</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://www.privateequityinternational.com/institution-profiles/veteran-ventures-capital.html, https://www.privateequityinternational.com/contact-us/, https://www.privateequityinternational.com/about-us/, https://www.privateequityinternational.com/database/institution-profile/id/institution:98mum/Veteran Ventures Capital/gp-contact-information</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>https://twitter.com/PEI_news</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1863062/000186306221000003/xslFormDX01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2604 LITTLE JOHN LANE, Austin, Texas, US</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Merged</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://sec.gov/Archives/edgar/data/2113209/000211320926000001/0002113209-26-000001-index.htm, https://www.sec.gov/Archives/edgar/data/1280776/000119380522001602/0001193805-22-001602-index.htm, https://www.sec.gov/Archives/edgar/data/1405788/000140578826000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1411494/000095014222002613/eh220282741_8k.htm, https://www.sec.gov/Archives/edgar/data/1421625/000090266422002100/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1579526/000131586326000081/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1587281/000162828025052166/0001628280-25-052166-index.html, https://www.sec.gov/Archives/edgar/data/1658949/000165894916000003/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1805645/000180564525000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1847068/000184706821000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1863062/000186306221000003/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1877061/000187706121000002/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1878313/000149315225018014/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1888787/000131586322000682/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1891022/000139372521000163/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1896430/000189643024000007/xslForm13F_X02/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1935068/000193506822000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1956026/000195602622000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1973673/000197367324000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/1999181/000199918123000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2028199/000202819924000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2041881/000204188124000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2043049/000204304924000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2069415/000206941525000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2072063/000207206326000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2101160/000210116026000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2108065/000210806526000001/0002108065-26-000001-index.htm, https://www.sec.gov/Archives/edgar/data/2112674/000211267426000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2113654/000211365426000001/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2113876/000095014226000631/xslFormDX01/primary_doc.xml, https://www.sec.gov/Archives/edgar/data/2129506/000212950626000001/0002129506-26-000001-index.htm, https://www.sec.gov/Archives/edgar/data/354963/000117184326002650/f8k_042126.htm</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>https://cleartax.in/f/company/julia-computing-india-private-limited/U72200KA2015FTC080584</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>c/o JuliaHub, Bangalore, Karnataka, MA</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://cleartax.in/f/company/julia-computing-india-private-limited/U72200KA2015FTC080584</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>https://lawyers.findlaw.com/new-jersey/camden/2130747_1/review</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>150 N. Riverside Plaza, Camden, New Jersey, IL</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://lawyers.findlaw.com/new-jersey/camden/2130747_1/review</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>https://nai500.com/companies/metals100-featured-company-1911-gold-corporation</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>400 Burrard Street, Vancouver, British Columbia, A1</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://nai500.com/companies/metals100-featured-company-1911-gold-corporation</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>https://www.streetinsider.com/SEC+Filings/Form+DA+Catalio+Access+Fund+IX%2C/26747213.html</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Catalio Capital Management, New York, New York, NY</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Merged</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://www.streetinsider.com/SEC+Filings/Form+3+Blue+Owl+Digital+Infrast+For%3A+Jun+30+Filed+by%3A+Viellieu+Jack/26742939.html, https://www.streetinsider.com/SEC+Filings/Form+D+Committed+Advisors+Secon/25953992.html, https://www.streetinsider.com/SEC+Filings/Form+D+David+Capital+Partners/24285910.html, https://www.streetinsider.com/SEC+Filings/Form+D+Virtue+V2+LP/24211468.html, https://www.streetinsider.com/SEC+Filings/Form+D+Vivo+Opportunity+Co-Inve/26214602.html, https://www.streetinsider.com/SEC+Filings/Form+DA+Catalio+Access+Fund+IX%2C/26747213.html</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>https://reports.adviserinfo.sec.gov/reports/ADV/286371/PDF/286371.pdf</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>+13276800000</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>700 Canal Street, STAMFORD, Connecticut, US</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Merged</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://reports.adviserinfo.sec.gov/about, https://reports.adviserinfo.sec.gov/contact, https://reports.adviserinfo.sec.gov/contact-us, https://reports.adviserinfo.sec.gov/reports/ADV/286371/PDF/286371.pdf, https://reports.adviserinfo.sec.gov/reports/ADV/334352/PDF/334352.pdf</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>CONTACT</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>https://www.villagesearchpartners.com/contact</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>info@villagesearchpartners.com</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>1 Blackfield Drive Suite 122, San Francisco, California, US</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://www.villagesearchpartners.com/contact, https://www.villagesearchpartners.com/contact, https://www.villagesearchpartners.com/about, https://www.villagesearchpartners.com/team</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/village-search-partners/</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>https://capeannam.com</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>c/o Cape Ann Asset Management Limited, London, England, X0</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://capeannam.com</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>https://schneiderdowns.com/staff/michael-j-voinovich-cpa</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>9115 W. Russell Rd., Columbus, Ohio, NV</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://schneiderdowns.com/staff/michael-j-voinovich-cpa</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Suzanne Vogel, Clinical Social Work/Therapist, Richmond, VA, 23219</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>https://www.psychologytoday.com/us/therapists/suzanne-vogel-richmond-va/1181494</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>accessibility@psychologytoday.com</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>+16469564495, +18045677944</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>7 Wildwood Lane, Richmond, VA, US</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://www.psychologytoday.com/us/therapists/suzanne-vogel-richmond-va/1181494, https://www.psychologytoday.com/us/groups, https://www.psychologytoday.com/about, https://www.psychologytoday.com/us/accessibility-help</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Preply</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>https://tracxn.com/d/companies/preply/__NM3YeXRszSNk2UeGjGPFYxh0PCylpf6iBMYNRoUxW48</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>hi@tracxn.com</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>+919939090919</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>c/o Preply, Brookline, Massachusetts, MA</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://tracxn.com/d/companies/preply/__NM3YeXRszSNk2UeGjGPFYxh0PCylpf6iBMYNRoUxW48</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>https://facebook.com/preplycom</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>https://twitter.com/preplycom</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Robots.txt restricts crawling on https://tracxn.com/d/companies/preply/__NM3YeXRszSNk2UeGjGPFYxh0PCylpf6iBMYNRoUxW48.</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>https://www.bbb.org/us/fl/pembroke-pines/profile/cruises/villa-vie-residences-vvr-0633-92049901</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1413 SW 156th Way, Pembroke Pines, Florida, US</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://www.bbb.org/us/fl/pembroke-pines/profile/cruises/villa-vie-residences-vvr-0633-92049901</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Adam Vigna - Sagard</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>https://informaconnect.com/superreturn-international/speakers/adam-vigna</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>gf-registrations@informa.com, gfsupport@informa.com, lpsuperreturn@informa.com, michaela.virtue@informa.com, rachel.lewis@informa.com, sponsorsuperreturn@informa.com, stephen.ashiotis@informa.com</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>+442080520419, +442080522013, +447796421070, +447990007530</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>c/o Sagard Credit Partners III-U (US) LP, Toronto, Toronto, A6</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://informaconnect.com/superreturn-international/speakers/adam-vigna, https://informaconnect.com/superreturn-international/contact/, https://informaconnect.com/contact, https://informaconnect.com/contact-us</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/informa-connect/</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/InformaConnect/</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/InformaConnect</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>https://x.com/hashtag/SuperReturn/</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCWkO2zFvz3WJ4y3q9dsKOwQ/</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>https://www.johannavolpi200weststreetnewyork.com</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>200 West Street, 200 West Street, New York, US</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://www.johannavolpi200weststreetnewyork.com</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>https://www.georgevoigtsuite201newportbeachca.com</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>1500 Balboa Blvd., Suite #201, Newport Beach, CA</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://www.georgevoigtsuite201newportbeachca.com</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>https://www.villageraleighgpllcsuite320aventurafl.com</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>20803 Biscayne Boulevard, Suite 320, Aventura, FL</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://www.villageraleighgpllcsuite320aventurafl.com</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>https://www.rogervincent3rdfloornewyorkny.com</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>315 Madison Avenue, 3rd Floor, New York, NY</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://www.rogervincent3rdfloornewyorkny.com</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>https://www.villagesquarepartnersllcsuite100atlantaga.com</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>1952 Howell Mill Rd, Suite 100, Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://www.villagesquarepartnersllcsuite100atlantaga.com</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>https://www.santiagovillasuite300paloaltoca.com</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>c/o EFEX Inc., Suite 300, Palo Alto, CA</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://www.santiagovillasuite300paloaltoca.com</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>https://www.gabriellevitale2115lindwoodavenuefortlee.com</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2115 Lindwood Avenue, 2115 Lindwood Avenue, Fort Lee, US</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://www.gabriellevitale2115lindwoodavenuefortlee.com</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>https://www.vigilmanagementllcfloor2paloaltoca.com</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>2151 Park Blvd, Floor 2, Palo Alto, CA</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://www.vigilmanagementllcfloor2paloaltoca.com</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Biography</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>https://prospectivehealthllc.com/biography</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>paul.vonebers@prospectivehealthllc.com</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>3313 W. CHERRY LN. #640, Des Moines, Iowa, US</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://prospectivehealthllc.com/biography, https://prospectivehealthllc.com/contact-us/, https://prospectivehealthllc.com/health-care-providers/, https://prospectivehealthllc.com/contact</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>https://search.sunbiz.org/Inquiry/CorporationSearch/SearchResultDetail</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2029 Okeechobee Blvd, West Palm Beach, FL, FL</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://search.sunbiz.org/Inquiry/CorporationSearch/SearchResultDetail</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>https://www.katherineviscontiste2201880houstontx.com</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>17350 State Highway 249, Ste 220 #1880, Houston, TX</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://www.katherineviscontiste2201880houstontx.com</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>London Stock Exchange</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>https://www.londonstockexchange.com/news-article/LLOY/Board-Change/17072125</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>ZUIDPOOLSINGEL 2, London, ALPHEN AAN DEN RIJN, US</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://www.londonstockexchange.com/news-article/LLOY/Board-Change/17072125, https://www.londonstockexchange.com/contact, https://www.londonstockexchange.com/contact-us, https://www.londonstockexchange.com/about</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>https://www.virtaventuresgpiillc4thfloorsanfranciscoca.com</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>300 California St, 4th Floor, San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>https://www.virtaventuresgpiillc4thfloorsanfranciscoca.com</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>https://www.shreekkanthviswanathan36berkshirelanelincolnshire.com</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>36 Berkshire Lane, 36 Berkshire Lane, Lincolnshire, US</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>https://www.shreekkanthviswanathan36berkshirelanelincolnshire.com</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>http://www.columbia.edu/~dv2254</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>10900 RESEARCH BLVD, New York, New York, TX</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>http://www.columbia.edu/~dv2254</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>https://www.glennvisconti4936wsanrafaelsttampa.com</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>4936 W SAN RAFAEL ST, 4936 W SAN RAFAEL ST, TAMPA, US</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://www.glennvisconti4936wsanrafaelsttampa.com</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Cory Villaume</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>https://www.retailrealestatenetworkmn.com/contacts/cory-villaume</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>+16512266337, +19528883490</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>5201 Eden Avenue, Edina, MN, MN</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://www.retailrealestatenetworkmn.com/contacts/cory-villaume, https://www.retailrealestatenetworkmn.com/contact-us, https://www.retailrealestatenetworkmn.com/contacts/cory-villaume#content, https://www.retailrealestatenetworkmn.com/contacts/cory-villaume#join-modal</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/retail-real-estate-network-minnesota</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>https://crescentgrowthcapital.com/people/troy-villafarra-cfa</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>201 St. Charles Avenue, New Orleans, Louisiana, LA</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://crescentgrowthcapital.com/people/troy-villafarra-cfa</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Martin Vogel</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>https://irma.math.unistra.fr/~vogel</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Waystone Management Company (Lux) S.A., Strasbourg, France, N4</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://irma.math.unistra.fr/~vogel, https://irma.math.unistra.fr/teams/ana.html, https://irma.math.unistra.fr/contact, https://irma.math.unistra.fr/contact-us</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>https://www.vivocapitalxllc192lyttonavenuepaloalto.com</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>192 Lytton Avenue, 192 Lytton Avenue, Palo Alto, US</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://www.vivocapitalxllc192lyttonavenuepaloalto.com</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Crestview Partners</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>https://mergr.com/investor/crestview-partners/team</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>confidential@email.com, info@crestview.com</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>+12129060700</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>590 Madison Avenue, New York, NY, NY</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://mergr.com/investor/crestview-partners/team</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mergr</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Sports Management Worldwide</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>https://www.smwwagency.com/agent/jay-vinson</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>305 Mace Boulevard, Lithia Springs, Georgia, CA</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://www.smwwagency.com/agent/jay-vinson, https://www.smwwagency.com/contact, https://www.smwwagency.com/contact-us, https://www.smwwagency.com/about</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Official Cádiz CF staff in 2026/27</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>https://www.laliga.com/en-GB/clubs/cadiz-cf/squad</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>derechos@laliga.es</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>5015 Highway 59 N, Cadiz, Andalusia, US</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>https://www.laliga.com/en-GB/clubs/cadiz-cf/squad, https://www.laliga.com/en-GB/pressroom/contact, https://www.laliga.com/en-GB/leaderboard, https://www.laliga.com/en-GB/foundation/about-us</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/laliga/</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cadizclubdefutbol/?fref=ts</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>https://instagram.com/cadizclubdefutbol/</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>https://twitter.com/laligaEN</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/laliga</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Imprint</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>https://alpinespace.vc/imprint</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>team@alpinespace.vc</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>c/o Alpine Space Ventures Mgmt.GmbH, Munich, Munich, 2M</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>https://alpinespace.vc/imprint, https://alpinespace.vc/imprint#team, https://alpinespace.vc/contact, https://alpinespace.vc/contact-us</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Vireon Ventures</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>https://www.vireon.ventures</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2950 Sunny Hill Lane, Dallas, Texas, US</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://www.vireon.ventures, https://www.vireon.ventures/contact, https://www.vireon.ventures/contact-us, https://www.vireon.ventures/about</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vireon-ventures</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Bain Capital</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>https://www.baincapital.com/people/andrew-s-viens</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ir@baincapital.com, positions@bankboston.educat</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>+12123269420, +12124212225, +12128222900, +13122536940, +16175162000, +16175162010, +16282013600, +16507982500, +2304681320, +2304681321, +35227942930, +35316335380, +35319019800, +442075145250, +442075145252, +4989244410700, +4989244410731, +61290935500, +61381028600, +6560161030, +81362127070, +81362127071, +81677122777, +82263229822, +82269402300, +85230140844, +85236566800, +862160626120, +862180121700, +912267528000</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>C/O BAIN CAPITAL CREDIT, Boston, Massachusetts, MA</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://www.baincapital.com/people/andrew-s-viens, https://www.baincapital.com/about-us, https://www.baincapital.com/about-us#overview, https://www.baincapital.com/about-us#purposeandValue</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bain-capital</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>https://twitter.com/baincapital?lang=en</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>https://www.naushadvirjisuite2291lakemaryfl.com</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>1331 S. International Parkway, Suite 2291, Lake Mary, FL</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://www.naushadvirjisuite2291lakemaryfl.com</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>https://www.sallyvincentsuite200goldenco.com</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>17560 S. Golden Road, Suite 200, Golden, CO</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://www.sallyvincentsuite200goldenco.com</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Von Bergen, MD, Nicholas (Nick)</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>https://www.pediatrics.wisc.edu/staff/von-bergen-nicholas</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>webmaster@pediatrics.wisc.edu</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>+16082652236</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>455 Science Drive, Madison, WI, WI</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://www.pediatrics.wisc.edu/staff/von-bergen-nicholas</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wiscpedsres</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>https://twitter.com/WiscPediatrics</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Nelson Vieira</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>https://www.iadfrance.fr/en/real-estate-agent/nelson.vieira</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2040 Boston Road, Rueil-Malmaison, Wilbraham, MA</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://www.iadfrance.fr/en/real-estate-agent/nelson.vieira, https://www.iadfrance.fr/contact, https://www.iadfrance.fr/contact-us, https://www.iadfrance.fr/about</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr"/>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>https://www.josephvolpesuite600alexandriava.com</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>c/o TransVoyant, Suite 600, Alexandria, VA</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://www.josephvolpesuite600alexandriava.com</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Fund Companies Directory</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>https://privatefunddata.com/fund-companies/vip-capital-management-lp</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>hello@privatefunddata.com</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>152 West 57th Street, New York, New York, NY</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>1</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://privatefunddata.com/fund-companies/vip-capital-management-lp, https://privatefunddata.com/contact/, https://privatefunddata.com/contact, https://privatefunddata.com/contact-us</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>BrokerCheck</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>https://brokercheck.finra.org/individual/summary/5851551</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>4936 W SAN RAFAEL ST, Tampa, Florida, US</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://brokercheck.finra.org/individual/summary/5851551, https://brokercheck.finra.org/contact, https://brokercheck.finra.org/contact-us, https://brokercheck.finra.org/about</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Ep 56: Rytis Vitkauskas — The Pursuit of Scrappiness Podcast</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://www.pursuitofscrappiness.co/episodes/56-rytis-vitkauskas-lightspeed</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>rytis@lsvp.com</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>c/o Cube Security Inc., London, England, CA</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://www.pursuitofscrappiness.co/episodes/56-rytis-vitkauskas-lightspeed, https://www.pursuitofscrappiness.co/contact, https://www.pursuitofscrappiness.co/contact-us, https://www.pursuitofscrappiness.co/about</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pursuit-of-scrappiness/</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCP6ueaLnjS-CQfrMCm2EoTA</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>PEPF Overture Chapel Hill REIT, LLC</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://www.formds.com/issuers/pepf-overture-chapel-hill-reit-llc</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>+18005331390</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>801 GRAND AVENUE, Des Moines, IA, US</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://www.formds.com/issuers/pepf-overture-chapel-hill-reit-llc, https://www.formds.com/contact, https://www.formds.com/contact-us, https://www.formds.com/about</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "scraper", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>https://www.christophervisgiliosuite400sanfranciscoca.com</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>150 CALIFORNIA STREET, SUITE 400, SAN FRANCISCO, CA</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://www.christophervisgiliosuite400sanfranciscoca.com</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>https://www.vlatkovlatkovicsuite1000morrisvillenc.com</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>951 Aviation Parkway, Suite 1000, Morrisville, NC</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://www.vlatkovlatkovicsuite1000morrisvillenc.com</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr"/>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://www.karenvidela9218cypressgreendrivejacksonville.com</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>9218 Cypress Green Drive, 9218 Cypress Green Drive, Jacksonville, US</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://www.karenvidela9218cypressgreendrivejacksonville.com</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>VOLO VENTURES FUND II, LP Top 13F Holdings</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://whalewisdom.com/filer/volo-ventures-fund-ii-lp</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>contact@whalewisdom.com</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>160 NW UTICA AVE, Bend, Oregon, US</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://whalewisdom.com/filer/volo-ventures-fund-ii-lp, https://whalewisdom.com/contact, https://whalewisdom.com/whitepapers/whalewisdom, https://whalewisdom.com/about</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/whalewisdom13f/</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>https://twitter.com/whalewisdom</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://www.vipgpllc32ndfloornewyorkny.com</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>152 West 57th Street, 32nd Floor, New York, NY</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://www.vipgpllc32ndfloornewyorkny.com</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://www.virtuev2gp2604littlejohnlaneaustin.com</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>2604 LITTLE JOHN LANE, 2604 LITTLE JOHN LANE, AUSTIN, US</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://www.virtuev2gp2604littlejohnlaneaustin.com</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>https://www.villagesearchpartnersfundigpllc1blackfielddrivesuite122tiburon.com</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>1 Blackfield Drive Suite 122, 1 Blackfield Drive Suite 122, Tiburon, US</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://www.villagesearchpartnersfundigpllc1blackfielddrivesuite122tiburon.com</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://www.katievilasuite630boiseid.com</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>1100 W IDAHO STREET, SUITE 630, BOISE, ID</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://www.katievilasuite630boiseid.com</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Michelangelo Achille Volpi's Profile</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://profiles.stanford.edu/michelangelo-volpi</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>cadami@stanford.edu, mohamedabdelmonem@stanfordhealthcare.org, mvolpi@stanford.edu, oabdelha@stanford.edu</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>524 HAMILTON AVENUE, Stanford, California, CA</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://profiles.stanford.edu/michelangelo-volpi, https://profiles.stanford.edu/browse/office-of-external-relations, https://profiles.stanford.edu/browse/office-of-vp-for-university-human-resources, https://profiles.stanford.edu/browse/office-of-vice-president-for-business-affairs-and-chief-financial-officer</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "scraper", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://www.fredvoccolasuite250knoxvilletn.com</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>2035 Lakeside Centre Way, Suite 250, Knoxville, TN</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://www.fredvoccolasuite250knoxvilletn.com</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>HTTP homepage failed: Failed after 4 attempts. Last error: [Errno 11001] getaddrinfo failed; AI Enrichment Error: No AI providers available for structured query.</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>{"business_name": "scraper", "emails": "", "phones": "", "address": "importer"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
